--- a/manual/MFEP_Wisata_Gastronomi_Surakarta (1).xlsx
+++ b/manual/MFEP_Wisata_Gastronomi_Surakarta (1).xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angga\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5C1993-E4BB-46AD-BF4F-D7BFB3EF97D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Cover &amp; Penjelasan" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Analisis Sensitivitas" sheetId="5" r:id="rId5"/>
     <sheet name="Hasil &amp; Rekomendasi" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="144525" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1002,7 +996,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -1391,48 +1385,6 @@
   </cellStyleXfs>
   <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1734,9 +1686,69 @@
     <xf numFmtId="165" fontId="24" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1744,24 +1756,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2027,7 +2021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2038,155 +2032,155 @@
   <sheetData>
     <row r="1" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
     </row>
     <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="104"/>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+      <c r="A14" s="4">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
+      <c r="A15" s="4">
         <v>2</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
+      <c r="A16" s="4">
         <v>3</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18">
+      <c r="A17" s="4">
         <v>4</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+      <c r="A18" s="4">
         <v>5</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2202,7 +2196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2215,292 +2209,292 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
     </row>
     <row r="3" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="7">
         <v>0.25</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="8">
         <f t="shared" ref="F4:F9" si="0">E4/SUM($E$4:$E$9)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="11">
         <v>0.2</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="12">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="7">
         <v>0.15</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="8">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="11">
         <v>0.2</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="7">
         <v>0.1</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="11">
         <v>0.1</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="13">
         <f>SUM(E4:E9)</f>
         <v>1</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="14">
         <f>SUM(F4:F9)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="B12" s="110"/>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
     </row>
     <row r="14" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
     </row>
     <row r="15" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
     </row>
     <row r="16" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
+      <c r="A16" s="16">
         <v>1</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
     </row>
     <row r="17" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33">
+      <c r="A17" s="19">
         <v>2</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
     </row>
     <row r="18" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36">
+      <c r="A18" s="22">
         <v>3</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="106"/>
     </row>
     <row r="19" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39">
+      <c r="A19" s="25">
         <v>4</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="107" t="s">
         <v>82</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="107"/>
     </row>
     <row r="20" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="42">
+      <c r="A20" s="28">
         <v>5</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="108" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2520,7 +2514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2531,670 +2525,670 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
     </row>
     <row r="3" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="31" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="33">
         <v>5</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="33">
         <v>5</v>
       </c>
-      <c r="F4" s="47">
+      <c r="F4" s="33">
         <v>5</v>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="33">
         <v>5</v>
       </c>
-      <c r="H4" s="48">
+      <c r="H4" s="34">
         <v>4</v>
       </c>
-      <c r="I4" s="48">
+      <c r="I4" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="33">
         <v>5</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="33">
         <v>5</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="34">
         <v>4</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="33">
         <v>5</v>
       </c>
-      <c r="H5" s="48">
+      <c r="H5" s="34">
         <v>4</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="33">
         <v>5</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="33">
         <v>5</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="34">
         <v>4</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="34">
         <v>4</v>
       </c>
-      <c r="H6" s="48">
+      <c r="H6" s="34">
         <v>4</v>
       </c>
-      <c r="I6" s="48">
+      <c r="I6" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="34">
         <v>4</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="34">
         <v>4</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="33">
         <v>5</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="34">
         <v>4</v>
       </c>
-      <c r="H7" s="49">
+      <c r="H7" s="35">
         <v>3</v>
       </c>
-      <c r="I7" s="48">
+      <c r="I7" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="34">
         <v>4</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="34">
         <v>4</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="34">
         <v>4</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="34">
         <v>4</v>
       </c>
-      <c r="H8" s="47">
+      <c r="H8" s="33">
         <v>5</v>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="34">
         <v>4</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="33">
         <v>5</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="33">
         <v>5</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="34">
         <v>4</v>
       </c>
-      <c r="H9" s="47">
+      <c r="H9" s="33">
         <v>5</v>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="34">
         <v>4</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="34">
         <v>4</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="34">
         <v>4</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="34">
         <v>4</v>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="35">
         <v>3</v>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="33">
         <v>5</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="33">
         <v>5</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="34">
         <v>4</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="34">
         <v>4</v>
       </c>
-      <c r="H11" s="47">
+      <c r="H11" s="33">
         <v>5</v>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="33">
         <v>5</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="34">
         <v>4</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="35">
         <v>3</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="35">
         <v>3</v>
       </c>
-      <c r="H12" s="48">
+      <c r="H12" s="34">
         <v>4</v>
       </c>
-      <c r="I12" s="49">
+      <c r="I12" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="34">
         <v>4</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="34">
         <v>4</v>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="33">
         <v>5</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="34">
         <v>4</v>
       </c>
-      <c r="H13" s="49">
+      <c r="H13" s="35">
         <v>3</v>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="33">
         <v>5</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="33">
         <v>5</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="34">
         <v>4</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="33">
         <v>5</v>
       </c>
-      <c r="H14" s="48">
+      <c r="H14" s="34">
         <v>4</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="33">
         <v>5</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="33">
         <v>5</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="35">
         <v>3</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="35">
         <v>3</v>
       </c>
-      <c r="H15" s="48">
+      <c r="H15" s="34">
         <v>4</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="35">
         <v>3</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="34">
         <v>4</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="33">
         <v>5</v>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="34">
         <v>4</v>
       </c>
-      <c r="H16" s="49">
+      <c r="H16" s="35">
         <v>3</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="34">
         <v>4</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="34">
         <v>4</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="34">
         <v>4</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="34">
         <v>4</v>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="34">
         <v>4</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="33">
         <v>5</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="33">
         <v>5</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="35">
         <v>3</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="35">
         <v>3</v>
       </c>
-      <c r="H18" s="47">
+      <c r="H18" s="33">
         <v>5</v>
       </c>
-      <c r="I18" s="49">
+      <c r="I18" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="33">
         <v>5</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="33">
         <v>5</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="35">
         <v>3</v>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="34">
         <v>4</v>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="34">
         <v>4</v>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="34">
         <v>4</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="34">
         <v>4</v>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="34">
         <v>4</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="34">
         <v>4</v>
       </c>
-      <c r="H20" s="49">
+      <c r="H20" s="35">
         <v>3</v>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="33">
         <v>5</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="33">
         <v>5</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="35">
         <v>3</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="34">
         <v>4</v>
       </c>
-      <c r="H21" s="48">
+      <c r="H21" s="34">
         <v>4</v>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="35">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="33">
         <v>5</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="33">
         <v>5</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="34">
         <v>4</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="34">
         <v>4</v>
       </c>
-      <c r="H22" s="48">
+      <c r="H22" s="34">
         <v>4</v>
       </c>
-      <c r="I22" s="48">
+      <c r="I22" s="34">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="48">
+      <c r="D23" s="34">
         <v>4</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="33">
         <v>5</v>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="34">
         <v>4</v>
       </c>
-      <c r="G23" s="47">
+      <c r="G23" s="33">
         <v>5</v>
       </c>
-      <c r="H23" s="47">
+      <c r="H23" s="33">
         <v>5</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="51" t="s">
+      <c r="A24" s="36"/>
+      <c r="B24" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="52">
+      <c r="C24" s="36"/>
+      <c r="D24" s="38">
         <f t="shared" ref="D24:I24" si="0">MAX(D4:D23)</f>
         <v>5</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F24" s="52">
+      <c r="F24" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H24" s="52">
+      <c r="H24" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I24" s="52">
+      <c r="I24" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="110" t="s">
         <v>156</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
+      <c r="B26" s="110"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3207,7 +3201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3218,1473 +3212,1473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="109" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
     </row>
     <row r="2" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="113"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="114" t="s">
         <v>158</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="1" t="s">
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="2" t="s">
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="114" t="s">
         <v>160</v>
       </c>
-      <c r="P2" s="2"/>
+      <c r="P2" s="114"/>
     </row>
     <row r="3" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="L3" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="M3" s="45" t="s">
+      <c r="M3" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="N3" s="45" t="s">
+      <c r="N3" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="O3" s="54" t="s">
+      <c r="O3" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="41" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="58" t="s">
+      <c r="D4" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="45">
         <f>'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J4" s="59">
+      <c r="J4" s="45">
         <f>'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K4" s="59">
+      <c r="K4" s="45">
         <f>'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="L4" s="59">
+      <c r="L4" s="45">
         <f>'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.2</v>
       </c>
-      <c r="M4" s="59">
+      <c r="M4" s="45">
         <f>'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="N4" s="59">
+      <c r="N4" s="45">
         <f>'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.1</v>
       </c>
-      <c r="O4" s="60" t="s">
+      <c r="O4" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="P4" s="61" t="s">
+      <c r="P4" s="47" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="48">
         <f>'Data Destinasi'!D4/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="48">
         <f>'Data Destinasi'!E4/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="48">
         <f>'Data Destinasi'!F4/'Data Destinasi'!F24</f>
         <v>1</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="48">
         <f>'Data Destinasi'!G4/'Data Destinasi'!G24</f>
         <v>1</v>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="48">
         <f>'Data Destinasi'!H4/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H5" s="62">
+      <c r="H5" s="48">
         <f>'Data Destinasi'!I4/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I5" s="63">
+      <c r="I5" s="49">
         <f>C5*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J5" s="63">
+      <c r="J5" s="49">
         <f>D5*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K5" s="63">
+      <c r="K5" s="49">
         <f>E5*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="L5" s="63">
+      <c r="L5" s="49">
         <f>F5*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.2</v>
       </c>
-      <c r="M5" s="63">
+      <c r="M5" s="49">
         <f>G5*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N5" s="63">
+      <c r="N5" s="49">
         <f>H5*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O5" s="64">
+      <c r="O5" s="50">
         <f t="shared" ref="O5:O25" si="0">SUM(I5:N5)</f>
         <v>0.96000000000000019</v>
       </c>
-      <c r="P5" s="65">
+      <c r="P5" s="51">
         <f t="shared" ref="P5:P24" si="1">RANK(O5,$O$5:$O$24,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="66">
+      <c r="C6" s="52">
         <f>'Data Destinasi'!D5/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D6" s="66">
+      <c r="D6" s="52">
         <f>'Data Destinasi'!E5/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E6" s="66">
+      <c r="E6" s="52">
         <f>'Data Destinasi'!F5/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F6" s="66">
+      <c r="F6" s="52">
         <f>'Data Destinasi'!G5/'Data Destinasi'!G24</f>
         <v>1</v>
       </c>
-      <c r="G6" s="66">
+      <c r="G6" s="52">
         <f>'Data Destinasi'!H5/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H6" s="66">
+      <c r="H6" s="52">
         <f>'Data Destinasi'!I5/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I6" s="67">
+      <c r="I6" s="53">
         <f>C6*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J6" s="67">
+      <c r="J6" s="53">
         <f>D6*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K6" s="67">
+      <c r="K6" s="53">
         <f>E6*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L6" s="67">
+      <c r="L6" s="53">
         <f>F6*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.2</v>
       </c>
-      <c r="M6" s="67">
+      <c r="M6" s="53">
         <f>G6*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N6" s="67">
+      <c r="N6" s="53">
         <f>H6*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="50">
         <f t="shared" si="0"/>
         <v>0.93000000000000016</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="51">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="48">
         <f>'Data Destinasi'!D6/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="48">
         <f>'Data Destinasi'!E6/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E7" s="62">
+      <c r="E7" s="48">
         <f>'Data Destinasi'!F6/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="48">
         <f>'Data Destinasi'!G6/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="48">
         <f>'Data Destinasi'!H6/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H7" s="62">
+      <c r="H7" s="48">
         <f>'Data Destinasi'!I6/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I7" s="63">
+      <c r="I7" s="49">
         <f>C7*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J7" s="63">
+      <c r="J7" s="49">
         <f>D7*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K7" s="63">
+      <c r="K7" s="49">
         <f>E7*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L7" s="63">
+      <c r="L7" s="49">
         <f>F7*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M7" s="63">
+      <c r="M7" s="49">
         <f>G7*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N7" s="63">
+      <c r="N7" s="49">
         <f>H7*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O7" s="64">
+      <c r="O7" s="50">
         <f t="shared" si="0"/>
         <v>0.89000000000000012</v>
       </c>
-      <c r="P7" s="65">
+      <c r="P7" s="51">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="52">
         <f>'Data Destinasi'!D7/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D8" s="66">
+      <c r="D8" s="52">
         <f>'Data Destinasi'!E7/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E8" s="66">
+      <c r="E8" s="52">
         <f>'Data Destinasi'!F7/'Data Destinasi'!F24</f>
         <v>1</v>
       </c>
-      <c r="F8" s="66">
+      <c r="F8" s="52">
         <f>'Data Destinasi'!G7/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G8" s="66">
+      <c r="G8" s="52">
         <f>'Data Destinasi'!H7/'Data Destinasi'!H24</f>
         <v>0.6</v>
       </c>
-      <c r="H8" s="66">
+      <c r="H8" s="52">
         <f>'Data Destinasi'!I7/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I8" s="67">
+      <c r="I8" s="53">
         <f>C8*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="53">
         <f>D8*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="53">
         <f>E8*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="L8" s="67">
+      <c r="L8" s="53">
         <f>F8*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M8" s="67">
+      <c r="M8" s="53">
         <f>G8*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.06</v>
       </c>
-      <c r="N8" s="67">
+      <c r="N8" s="53">
         <f>H8*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O8" s="64">
+      <c r="O8" s="50">
         <f t="shared" si="0"/>
         <v>0.81</v>
       </c>
-      <c r="P8" s="65">
+      <c r="P8" s="51">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="62">
+      <c r="C9" s="48">
         <f>'Data Destinasi'!D8/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="48">
         <f>'Data Destinasi'!E8/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="48">
         <f>'Data Destinasi'!F8/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="48">
         <f>'Data Destinasi'!G8/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="48">
         <f>'Data Destinasi'!H8/'Data Destinasi'!H24</f>
         <v>1</v>
       </c>
-      <c r="H9" s="62">
+      <c r="H9" s="48">
         <f>'Data Destinasi'!I8/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I9" s="63">
+      <c r="I9" s="49">
         <f>C9*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J9" s="63">
+      <c r="J9" s="49">
         <f>D9*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K9" s="63">
+      <c r="K9" s="49">
         <f>E9*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L9" s="63">
+      <c r="L9" s="49">
         <f>F9*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M9" s="63">
+      <c r="M9" s="49">
         <f>G9*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="N9" s="63">
+      <c r="N9" s="49">
         <f>H9*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O9" s="64">
+      <c r="O9" s="50">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="P9" s="65">
+      <c r="P9" s="51">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="66">
+      <c r="C10" s="52">
         <f>'Data Destinasi'!D9/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D10" s="66">
+      <c r="D10" s="52">
         <f>'Data Destinasi'!E9/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E10" s="66">
+      <c r="E10" s="52">
         <f>'Data Destinasi'!F9/'Data Destinasi'!F24</f>
         <v>1</v>
       </c>
-      <c r="F10" s="66">
+      <c r="F10" s="52">
         <f>'Data Destinasi'!G9/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G10" s="66">
+      <c r="G10" s="52">
         <f>'Data Destinasi'!H9/'Data Destinasi'!H24</f>
         <v>1</v>
       </c>
-      <c r="H10" s="66">
+      <c r="H10" s="52">
         <f>'Data Destinasi'!I9/'Data Destinasi'!I24</f>
         <v>1</v>
       </c>
-      <c r="I10" s="67">
+      <c r="I10" s="53">
         <f>C10*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J10" s="67">
+      <c r="J10" s="53">
         <f>D10*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K10" s="67">
+      <c r="K10" s="53">
         <f>E10*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="L10" s="67">
+      <c r="L10" s="53">
         <f>F10*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M10" s="67">
+      <c r="M10" s="53">
         <f>G10*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="N10" s="67">
+      <c r="N10" s="53">
         <f>H10*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.1</v>
       </c>
-      <c r="O10" s="64">
+      <c r="O10" s="50">
         <f t="shared" si="0"/>
         <v>0.91</v>
       </c>
-      <c r="P10" s="65">
+      <c r="P10" s="51">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="62">
+      <c r="C11" s="48">
         <f>'Data Destinasi'!D10/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="48">
         <f>'Data Destinasi'!E10/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E11" s="62">
+      <c r="E11" s="48">
         <f>'Data Destinasi'!F10/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F11" s="62">
+      <c r="F11" s="48">
         <f>'Data Destinasi'!G10/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="48">
         <f>'Data Destinasi'!H10/'Data Destinasi'!H24</f>
         <v>0.6</v>
       </c>
-      <c r="H11" s="62">
+      <c r="H11" s="48">
         <f>'Data Destinasi'!I10/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I11" s="63">
+      <c r="I11" s="49">
         <f>C11*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J11" s="63">
+      <c r="J11" s="49">
         <f>D11*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K11" s="63">
+      <c r="K11" s="49">
         <f>E11*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L11" s="63">
+      <c r="L11" s="49">
         <f>F11*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M11" s="63">
+      <c r="M11" s="49">
         <f>G11*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.06</v>
       </c>
-      <c r="N11" s="63">
+      <c r="N11" s="49">
         <f>H11*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O11" s="64">
+      <c r="O11" s="50">
         <f t="shared" si="0"/>
         <v>0.76000000000000023</v>
       </c>
-      <c r="P11" s="65">
+      <c r="P11" s="51">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="66">
+      <c r="C12" s="52">
         <f>'Data Destinasi'!D11/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="52">
         <f>'Data Destinasi'!E11/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="52">
         <f>'Data Destinasi'!F11/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F12" s="66">
+      <c r="F12" s="52">
         <f>'Data Destinasi'!G11/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G12" s="66">
+      <c r="G12" s="52">
         <f>'Data Destinasi'!H11/'Data Destinasi'!H24</f>
         <v>1</v>
       </c>
-      <c r="H12" s="66">
+      <c r="H12" s="52">
         <f>'Data Destinasi'!I11/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I12" s="67">
+      <c r="I12" s="53">
         <f>C12*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J12" s="67">
+      <c r="J12" s="53">
         <f>D12*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K12" s="67">
+      <c r="K12" s="53">
         <f>E12*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L12" s="67">
+      <c r="L12" s="53">
         <f>F12*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M12" s="67">
+      <c r="M12" s="53">
         <f>G12*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="N12" s="67">
+      <c r="N12" s="53">
         <f>H12*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O12" s="64">
+      <c r="O12" s="50">
         <f t="shared" si="0"/>
         <v>0.89000000000000012</v>
       </c>
-      <c r="P12" s="65">
+      <c r="P12" s="51">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="62">
+      <c r="C13" s="48">
         <f>'Data Destinasi'!D12/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="48">
         <f>'Data Destinasi'!E12/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E13" s="62">
+      <c r="E13" s="48">
         <f>'Data Destinasi'!F12/'Data Destinasi'!F24</f>
         <v>0.6</v>
       </c>
-      <c r="F13" s="62">
+      <c r="F13" s="48">
         <f>'Data Destinasi'!G12/'Data Destinasi'!G24</f>
         <v>0.6</v>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="48">
         <f>'Data Destinasi'!H12/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H13" s="62">
+      <c r="H13" s="48">
         <f>'Data Destinasi'!I12/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I13" s="63">
+      <c r="I13" s="49">
         <f>C13*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J13" s="63">
+      <c r="J13" s="49">
         <f>D13*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K13" s="63">
+      <c r="K13" s="49">
         <f>E13*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.09</v>
       </c>
-      <c r="L13" s="63">
+      <c r="L13" s="49">
         <f>F13*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.12</v>
       </c>
-      <c r="M13" s="63">
+      <c r="M13" s="49">
         <f>G13*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N13" s="63">
+      <c r="N13" s="49">
         <f>H13*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O13" s="64">
+      <c r="O13" s="50">
         <f t="shared" si="0"/>
         <v>0.76</v>
       </c>
-      <c r="P13" s="65">
+      <c r="P13" s="51">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="66">
+      <c r="C14" s="52">
         <f>'Data Destinasi'!D13/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D14" s="52">
         <f>'Data Destinasi'!E13/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E14" s="66">
+      <c r="E14" s="52">
         <f>'Data Destinasi'!F13/'Data Destinasi'!F24</f>
         <v>1</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="52">
         <f>'Data Destinasi'!G13/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="52">
         <f>'Data Destinasi'!H13/'Data Destinasi'!H24</f>
         <v>0.6</v>
       </c>
-      <c r="H14" s="66">
+      <c r="H14" s="52">
         <f>'Data Destinasi'!I13/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I14" s="67">
+      <c r="I14" s="53">
         <f>C14*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J14" s="67">
+      <c r="J14" s="53">
         <f>D14*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="53">
         <f>E14*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="L14" s="67">
+      <c r="L14" s="53">
         <f>F14*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M14" s="67">
+      <c r="M14" s="53">
         <f>G14*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.06</v>
       </c>
-      <c r="N14" s="67">
+      <c r="N14" s="53">
         <f>H14*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O14" s="64">
+      <c r="O14" s="50">
         <f t="shared" si="0"/>
         <v>0.81</v>
       </c>
-      <c r="P14" s="65">
+      <c r="P14" s="51">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="62">
+      <c r="C15" s="48">
         <f>'Data Destinasi'!D14/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="48">
         <f>'Data Destinasi'!E14/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E15" s="62">
+      <c r="E15" s="48">
         <f>'Data Destinasi'!F14/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="48">
         <f>'Data Destinasi'!G14/'Data Destinasi'!G24</f>
         <v>1</v>
       </c>
-      <c r="G15" s="62">
+      <c r="G15" s="48">
         <f>'Data Destinasi'!H14/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H15" s="62">
+      <c r="H15" s="48">
         <f>'Data Destinasi'!I14/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="49">
         <f>C15*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J15" s="63">
+      <c r="J15" s="49">
         <f>D15*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K15" s="63">
+      <c r="K15" s="49">
         <f>E15*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L15" s="63">
+      <c r="L15" s="49">
         <f>F15*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.2</v>
       </c>
-      <c r="M15" s="63">
+      <c r="M15" s="49">
         <f>G15*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N15" s="63">
+      <c r="N15" s="49">
         <f>H15*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O15" s="64">
+      <c r="O15" s="50">
         <f t="shared" si="0"/>
         <v>0.93000000000000016</v>
       </c>
-      <c r="P15" s="65">
+      <c r="P15" s="51">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="66">
+      <c r="C16" s="52">
         <f>'Data Destinasi'!D15/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D16" s="66">
+      <c r="D16" s="52">
         <f>'Data Destinasi'!E15/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="52">
         <f>'Data Destinasi'!F15/'Data Destinasi'!F24</f>
         <v>0.6</v>
       </c>
-      <c r="F16" s="66">
+      <c r="F16" s="52">
         <f>'Data Destinasi'!G15/'Data Destinasi'!G24</f>
         <v>0.6</v>
       </c>
-      <c r="G16" s="66">
+      <c r="G16" s="52">
         <f>'Data Destinasi'!H15/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H16" s="66">
+      <c r="H16" s="52">
         <f>'Data Destinasi'!I15/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I16" s="67">
+      <c r="I16" s="53">
         <f>C16*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J16" s="67">
+      <c r="J16" s="53">
         <f>D16*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K16" s="67">
+      <c r="K16" s="53">
         <f>E16*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.09</v>
       </c>
-      <c r="L16" s="67">
+      <c r="L16" s="53">
         <f>F16*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.12</v>
       </c>
-      <c r="M16" s="67">
+      <c r="M16" s="53">
         <f>G16*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N16" s="67">
+      <c r="N16" s="53">
         <f>H16*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O16" s="64">
+      <c r="O16" s="50">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="P16" s="65">
+      <c r="P16" s="51">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="62">
+      <c r="C17" s="48">
         <f>'Data Destinasi'!D16/'Data Destinasi'!D24</f>
         <v>0.6</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="48">
         <f>'Data Destinasi'!E16/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E17" s="62">
+      <c r="E17" s="48">
         <f>'Data Destinasi'!F16/'Data Destinasi'!F24</f>
         <v>1</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="48">
         <f>'Data Destinasi'!G16/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G17" s="62">
+      <c r="G17" s="48">
         <f>'Data Destinasi'!H16/'Data Destinasi'!H24</f>
         <v>0.6</v>
       </c>
-      <c r="H17" s="62">
+      <c r="H17" s="48">
         <f>'Data Destinasi'!I16/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="49">
         <f>C17*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.15</v>
       </c>
-      <c r="J17" s="63">
+      <c r="J17" s="49">
         <f>D17*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K17" s="63">
+      <c r="K17" s="49">
         <f>E17*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="L17" s="63">
+      <c r="L17" s="49">
         <f>F17*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M17" s="63">
+      <c r="M17" s="49">
         <f>G17*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.06</v>
       </c>
-      <c r="N17" s="63">
+      <c r="N17" s="49">
         <f>H17*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O17" s="64">
+      <c r="O17" s="50">
         <f t="shared" si="0"/>
         <v>0.76000000000000023</v>
       </c>
-      <c r="P17" s="65">
+      <c r="P17" s="51">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="66">
+      <c r="C18" s="52">
         <f>'Data Destinasi'!D17/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D18" s="66">
+      <c r="D18" s="52">
         <f>'Data Destinasi'!E17/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E18" s="66">
+      <c r="E18" s="52">
         <f>'Data Destinasi'!F17/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F18" s="66">
+      <c r="F18" s="52">
         <f>'Data Destinasi'!G17/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G18" s="66">
+      <c r="G18" s="52">
         <f>'Data Destinasi'!H17/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H18" s="66">
+      <c r="H18" s="52">
         <f>'Data Destinasi'!I17/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I18" s="67">
+      <c r="I18" s="53">
         <f>C18*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J18" s="67">
+      <c r="J18" s="53">
         <f>D18*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K18" s="67">
+      <c r="K18" s="53">
         <f>E18*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L18" s="67">
+      <c r="L18" s="53">
         <f>F18*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M18" s="67">
+      <c r="M18" s="53">
         <f>G18*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N18" s="67">
+      <c r="N18" s="53">
         <f>H18*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O18" s="64">
+      <c r="O18" s="50">
         <f t="shared" si="0"/>
         <v>0.78000000000000025</v>
       </c>
-      <c r="P18" s="65">
+      <c r="P18" s="51">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="62">
+      <c r="C19" s="48">
         <f>'Data Destinasi'!D18/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D19" s="62">
+      <c r="D19" s="48">
         <f>'Data Destinasi'!E18/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E19" s="62">
+      <c r="E19" s="48">
         <f>'Data Destinasi'!F18/'Data Destinasi'!F24</f>
         <v>0.6</v>
       </c>
-      <c r="F19" s="62">
+      <c r="F19" s="48">
         <f>'Data Destinasi'!G18/'Data Destinasi'!G24</f>
         <v>0.6</v>
       </c>
-      <c r="G19" s="62">
+      <c r="G19" s="48">
         <f>'Data Destinasi'!H18/'Data Destinasi'!H24</f>
         <v>1</v>
       </c>
-      <c r="H19" s="62">
+      <c r="H19" s="48">
         <f>'Data Destinasi'!I18/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="49">
         <f>C19*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J19" s="63">
+      <c r="J19" s="49">
         <f>D19*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K19" s="63">
+      <c r="K19" s="49">
         <f>E19*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.09</v>
       </c>
-      <c r="L19" s="63">
+      <c r="L19" s="49">
         <f>F19*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.12</v>
       </c>
-      <c r="M19" s="63">
+      <c r="M19" s="49">
         <f>G19*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="N19" s="63">
+      <c r="N19" s="49">
         <f>H19*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O19" s="64">
+      <c r="O19" s="50">
         <f t="shared" si="0"/>
         <v>0.82000000000000006</v>
       </c>
-      <c r="P19" s="65">
+      <c r="P19" s="51">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="66">
+      <c r="C20" s="52">
         <f>'Data Destinasi'!D19/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="52">
         <f>'Data Destinasi'!E19/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="52">
         <f>'Data Destinasi'!F19/'Data Destinasi'!F24</f>
         <v>0.6</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="52">
         <f>'Data Destinasi'!G19/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="52">
         <f>'Data Destinasi'!H19/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H20" s="66">
+      <c r="H20" s="52">
         <f>'Data Destinasi'!I19/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I20" s="67">
+      <c r="I20" s="53">
         <f>C20*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J20" s="67">
+      <c r="J20" s="53">
         <f>D20*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K20" s="67">
+      <c r="K20" s="53">
         <f>E20*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.09</v>
       </c>
-      <c r="L20" s="67">
+      <c r="L20" s="53">
         <f>F20*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M20" s="67">
+      <c r="M20" s="53">
         <f>G20*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N20" s="67">
+      <c r="N20" s="53">
         <f>H20*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O20" s="64">
+      <c r="O20" s="50">
         <f t="shared" si="0"/>
         <v>0.84000000000000008</v>
       </c>
-      <c r="P20" s="65">
+      <c r="P20" s="51">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="62">
+      <c r="C21" s="48">
         <f>'Data Destinasi'!D20/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D21" s="48">
         <f>'Data Destinasi'!E20/'Data Destinasi'!E24</f>
         <v>0.8</v>
       </c>
-      <c r="E21" s="62">
+      <c r="E21" s="48">
         <f>'Data Destinasi'!F20/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F21" s="62">
+      <c r="F21" s="48">
         <f>'Data Destinasi'!G20/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G21" s="62">
+      <c r="G21" s="48">
         <f>'Data Destinasi'!H20/'Data Destinasi'!H24</f>
         <v>0.6</v>
       </c>
-      <c r="H21" s="62">
+      <c r="H21" s="48">
         <f>'Data Destinasi'!I20/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I21" s="63">
+      <c r="I21" s="49">
         <f>C21*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J21" s="63">
+      <c r="J21" s="49">
         <f>D21*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="K21" s="63">
+      <c r="K21" s="49">
         <f>E21*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L21" s="63">
+      <c r="L21" s="49">
         <f>F21*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M21" s="63">
+      <c r="M21" s="49">
         <f>G21*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.06</v>
       </c>
-      <c r="N21" s="63">
+      <c r="N21" s="49">
         <f>H21*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O21" s="64">
+      <c r="O21" s="50">
         <f t="shared" si="0"/>
         <v>0.76000000000000023</v>
       </c>
-      <c r="P21" s="65">
+      <c r="P21" s="51">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="66">
+      <c r="C22" s="52">
         <f>'Data Destinasi'!D21/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="52">
         <f>'Data Destinasi'!E21/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="52">
         <f>'Data Destinasi'!F21/'Data Destinasi'!F24</f>
         <v>0.6</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="52">
         <f>'Data Destinasi'!G21/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G22" s="52">
         <f>'Data Destinasi'!H21/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H22" s="66">
+      <c r="H22" s="52">
         <f>'Data Destinasi'!I21/'Data Destinasi'!I24</f>
         <v>0.6</v>
       </c>
-      <c r="I22" s="67">
+      <c r="I22" s="53">
         <f>C22*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J22" s="67">
+      <c r="J22" s="53">
         <f>D22*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K22" s="67">
+      <c r="K22" s="53">
         <f>E22*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.09</v>
       </c>
-      <c r="L22" s="67">
+      <c r="L22" s="53">
         <f>F22*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M22" s="67">
+      <c r="M22" s="53">
         <f>G22*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N22" s="67">
+      <c r="N22" s="53">
         <f>H22*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.06</v>
       </c>
-      <c r="O22" s="64">
+      <c r="O22" s="50">
         <f t="shared" si="0"/>
         <v>0.84000000000000008</v>
       </c>
-      <c r="P22" s="65">
+      <c r="P22" s="51">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="62">
+      <c r="C23" s="48">
         <f>'Data Destinasi'!D22/'Data Destinasi'!D24</f>
         <v>1</v>
       </c>
-      <c r="D23" s="62">
+      <c r="D23" s="48">
         <f>'Data Destinasi'!E22/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E23" s="62">
+      <c r="E23" s="48">
         <f>'Data Destinasi'!F22/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="48">
         <f>'Data Destinasi'!G22/'Data Destinasi'!G24</f>
         <v>0.8</v>
       </c>
-      <c r="G23" s="62">
+      <c r="G23" s="48">
         <f>'Data Destinasi'!H22/'Data Destinasi'!H24</f>
         <v>0.8</v>
       </c>
-      <c r="H23" s="62">
+      <c r="H23" s="48">
         <f>'Data Destinasi'!I22/'Data Destinasi'!I24</f>
         <v>0.8</v>
       </c>
-      <c r="I23" s="63">
+      <c r="I23" s="49">
         <f>C23*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J23" s="63">
+      <c r="J23" s="49">
         <f>D23*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K23" s="63">
+      <c r="K23" s="49">
         <f>E23*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L23" s="63">
+      <c r="L23" s="49">
         <f>F23*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.16000000000000003</v>
       </c>
-      <c r="M23" s="63">
+      <c r="M23" s="49">
         <f>G23*'Data Kriteria &amp; Bobot'!E8</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="N23" s="63">
+      <c r="N23" s="49">
         <f>H23*'Data Kriteria &amp; Bobot'!E9</f>
         <v>8.0000000000000016E-2</v>
       </c>
-      <c r="O23" s="64">
+      <c r="O23" s="50">
         <f t="shared" si="0"/>
         <v>0.89000000000000012</v>
       </c>
-      <c r="P23" s="65">
+      <c r="P23" s="51">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="66">
+      <c r="C24" s="52">
         <f>'Data Destinasi'!D23/'Data Destinasi'!D24</f>
         <v>0.8</v>
       </c>
-      <c r="D24" s="66">
+      <c r="D24" s="52">
         <f>'Data Destinasi'!E23/'Data Destinasi'!E24</f>
         <v>1</v>
       </c>
-      <c r="E24" s="66">
+      <c r="E24" s="52">
         <f>'Data Destinasi'!F23/'Data Destinasi'!F24</f>
         <v>0.8</v>
       </c>
-      <c r="F24" s="66">
+      <c r="F24" s="52">
         <f>'Data Destinasi'!G23/'Data Destinasi'!G24</f>
         <v>1</v>
       </c>
-      <c r="G24" s="66">
+      <c r="G24" s="52">
         <f>'Data Destinasi'!H23/'Data Destinasi'!H24</f>
         <v>1</v>
       </c>
-      <c r="H24" s="66">
+      <c r="H24" s="52">
         <f>'Data Destinasi'!I23/'Data Destinasi'!I24</f>
         <v>1</v>
       </c>
-      <c r="I24" s="67">
+      <c r="I24" s="53">
         <f>C24*'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.2</v>
       </c>
-      <c r="J24" s="67">
+      <c r="J24" s="53">
         <f>D24*'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K24" s="67">
+      <c r="K24" s="53">
         <f>E24*'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.12</v>
       </c>
-      <c r="L24" s="67">
+      <c r="L24" s="53">
         <f>F24*'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.2</v>
       </c>
-      <c r="M24" s="67">
+      <c r="M24" s="53">
         <f>G24*'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="N24" s="67">
+      <c r="N24" s="53">
         <f>H24*'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.1</v>
       </c>
-      <c r="O24" s="64">
+      <c r="O24" s="50">
         <f t="shared" si="0"/>
         <v>0.91999999999999993</v>
       </c>
-      <c r="P24" s="65">
+      <c r="P24" s="51">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="68"/>
-      <c r="B25" s="51" t="s">
+      <c r="A25" s="54"/>
+      <c r="B25" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="27">
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="13">
         <f>'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="13">
         <f>'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="K25" s="27">
+      <c r="K25" s="13">
         <f>'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="L25" s="27">
+      <c r="L25" s="13">
         <f>'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.2</v>
       </c>
-      <c r="M25" s="27">
+      <c r="M25" s="13">
         <f>'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="N25" s="27">
+      <c r="N25" s="13">
         <f>'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.1</v>
       </c>
-      <c r="O25" s="69">
+      <c r="O25" s="55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P25" s="68"/>
+      <c r="P25" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4700,7 +4694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4710,23 +4704,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="109" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
     </row>
     <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="116" t="s">
@@ -4748,1627 +4742,1627 @@
       <c r="O2" s="116"/>
     </row>
     <row r="4" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="104" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="104"/>
     </row>
     <row r="5" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="I5" s="45" t="s">
+      <c r="I5" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="K5" s="45" t="s">
+      <c r="K5" s="31" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="56">
         <f>'Data Kriteria &amp; Bobot'!E4</f>
         <v>0.25</v>
       </c>
-      <c r="D6" s="71">
+      <c r="D6" s="57">
         <f>C6*(1+1*0.2)</f>
         <v>0.3</v>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="48">
         <f>C6*(1-$C$7*1*0.2)/(1-$C$7)</f>
         <v>0.3</v>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="48">
         <f>C6*(1-$C$8*1*0.2)/(1-$C$8)</f>
         <v>0.28529411764705881</v>
       </c>
-      <c r="G6" s="62">
+      <c r="G6" s="48">
         <f>C6*(1-$C$9*1*0.2)/(1-$C$9)</f>
         <v>0.3</v>
       </c>
-      <c r="H6" s="62">
+      <c r="H6" s="48">
         <f>C6*(1-$C$10*1*0.2)/(1-$C$10)</f>
         <v>0.2722222222222222</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="48">
         <f>C6*(1-$C$11*1*0.2)/(1-$C$11)</f>
         <v>0.2722222222222222</v>
       </c>
-      <c r="J6" s="71">
+      <c r="J6" s="57">
         <f>C6*(1+-1*0.2)</f>
         <v>0.2</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="48">
         <f>C6*(1-$C$7*-1*0.2)/(1-$C$7)</f>
         <v>0.32500000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="72">
+      <c r="C7" s="58">
         <f>'Data Kriteria &amp; Bobot'!E5</f>
         <v>0.2</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="59">
         <f>C7*(1-$C$6*1*0.2)/(1-$C$6)</f>
         <v>0.25333333333333335</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="57">
         <f>C7*(1+1*0.2)</f>
         <v>0.24</v>
       </c>
-      <c r="F7" s="73">
+      <c r="F7" s="59">
         <f>C7*(1-$C$8*1*0.2)/(1-$C$8)</f>
         <v>0.22823529411764706</v>
       </c>
-      <c r="G7" s="73">
+      <c r="G7" s="59">
         <f>C7*(1-$C$9*1*0.2)/(1-$C$9)</f>
         <v>0.24</v>
       </c>
-      <c r="H7" s="73">
+      <c r="H7" s="59">
         <f>C7*(1-$C$10*1*0.2)/(1-$C$10)</f>
         <v>0.21777777777777779</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="59">
         <f>C7*(1-$C$11*1*0.2)/(1-$C$11)</f>
         <v>0.21777777777777779</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="59">
         <f>C7*(1-$C$6*-1*0.2)/(1-$C$6)</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="57">
         <f>C7*(1+-1*0.2)</f>
         <v>0.16000000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C8" s="70">
+      <c r="C8" s="56">
         <f>'Data Kriteria &amp; Bobot'!E6</f>
         <v>0.15</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="48">
         <f>C8*(1-$C$6*1*0.2)/(1-$C$6)</f>
         <v>0.18999999999999997</v>
       </c>
-      <c r="E8" s="62">
+      <c r="E8" s="48">
         <f>C8*(1-$C$7*1*0.2)/(1-$C$7)</f>
         <v>0.17999999999999997</v>
       </c>
-      <c r="F8" s="71">
+      <c r="F8" s="57">
         <f>C8*(1+1*0.2)</f>
         <v>0.18</v>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="48">
         <f>C8*(1-$C$9*1*0.2)/(1-$C$9)</f>
         <v>0.17999999999999997</v>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="48">
         <f>C8*(1-$C$10*1*0.2)/(1-$C$10)</f>
         <v>0.16333333333333333</v>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="48">
         <f>C8*(1-$C$11*1*0.2)/(1-$C$11)</f>
         <v>0.16333333333333333</v>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="48">
         <f>C8*(1-$C$6*-1*0.2)/(1-$C$6)</f>
         <v>0.21</v>
       </c>
-      <c r="K8" s="62">
+      <c r="K8" s="48">
         <f>C8*(1-$C$7*-1*0.2)/(1-$C$7)</f>
         <v>0.19499999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="72">
+      <c r="C9" s="58">
         <f>'Data Kriteria &amp; Bobot'!E7</f>
         <v>0.2</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="59">
         <f>C9*(1-$C$6*1*0.2)/(1-$C$6)</f>
         <v>0.25333333333333335</v>
       </c>
-      <c r="E9" s="73">
+      <c r="E9" s="59">
         <f>C9*(1-$C$7*1*0.2)/(1-$C$7)</f>
         <v>0.24</v>
       </c>
-      <c r="F9" s="73">
+      <c r="F9" s="59">
         <f>C9*(1-$C$8*1*0.2)/(1-$C$8)</f>
         <v>0.22823529411764706</v>
       </c>
-      <c r="G9" s="71">
+      <c r="G9" s="57">
         <f>C9*(1+1*0.2)</f>
         <v>0.24</v>
       </c>
-      <c r="H9" s="73">
+      <c r="H9" s="59">
         <f>C9*(1-$C$10*1*0.2)/(1-$C$10)</f>
         <v>0.21777777777777779</v>
       </c>
-      <c r="I9" s="73">
+      <c r="I9" s="59">
         <f>C9*(1-$C$11*1*0.2)/(1-$C$11)</f>
         <v>0.21777777777777779</v>
       </c>
-      <c r="J9" s="73">
+      <c r="J9" s="59">
         <f>C9*(1-$C$6*-1*0.2)/(1-$C$6)</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="K9" s="73">
+      <c r="K9" s="59">
         <f>C9*(1-$C$7*-1*0.2)/(1-$C$7)</f>
         <v>0.26</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C10" s="70">
+      <c r="C10" s="56">
         <f>'Data Kriteria &amp; Bobot'!E8</f>
         <v>0.1</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="48">
         <f>C10*(1-$C$6*1*0.2)/(1-$C$6)</f>
         <v>0.12666666666666668</v>
       </c>
-      <c r="E10" s="62">
+      <c r="E10" s="48">
         <f>C10*(1-$C$7*1*0.2)/(1-$C$7)</f>
         <v>0.12</v>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="48">
         <f>C10*(1-$C$8*1*0.2)/(1-$C$8)</f>
         <v>0.11411764705882353</v>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="48">
         <f>C10*(1-$C$9*1*0.2)/(1-$C$9)</f>
         <v>0.12</v>
       </c>
-      <c r="H10" s="71">
+      <c r="H10" s="57">
         <f>C10*(1+1*0.2)</f>
         <v>0.12</v>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="48">
         <f>C10*(1-$C$11*1*0.2)/(1-$C$11)</f>
         <v>0.1088888888888889</v>
       </c>
-      <c r="J10" s="62">
+      <c r="J10" s="48">
         <f>C10*(1-$C$6*-1*0.2)/(1-$C$6)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="K10" s="62">
+      <c r="K10" s="48">
         <f>C10*(1-$C$7*-1*0.2)/(1-$C$7)</f>
         <v>0.13</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="72">
+      <c r="C11" s="58">
         <f>'Data Kriteria &amp; Bobot'!E9</f>
         <v>0.1</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="59">
         <f>C11*(1-$C$6*1*0.2)/(1-$C$6)</f>
         <v>0.12666666666666668</v>
       </c>
-      <c r="E11" s="73">
+      <c r="E11" s="59">
         <f>C11*(1-$C$7*1*0.2)/(1-$C$7)</f>
         <v>0.12</v>
       </c>
-      <c r="F11" s="73">
+      <c r="F11" s="59">
         <f>C11*(1-$C$8*1*0.2)/(1-$C$8)</f>
         <v>0.11411764705882353</v>
       </c>
-      <c r="G11" s="73">
+      <c r="G11" s="59">
         <f>C11*(1-$C$9*1*0.2)/(1-$C$9)</f>
         <v>0.12</v>
       </c>
-      <c r="H11" s="73">
+      <c r="H11" s="59">
         <f>C11*(1-$C$10*1*0.2)/(1-$C$10)</f>
         <v>0.1088888888888889</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="57">
         <f>C11*(1+1*0.2)</f>
         <v>0.12</v>
       </c>
-      <c r="J11" s="73">
+      <c r="J11" s="59">
         <f>C11*(1-$C$6*-1*0.2)/(1-$C$6)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="K11" s="73">
+      <c r="K11" s="59">
         <f>C11*(1-$C$7*-1*0.2)/(1-$C$7)</f>
         <v>0.13</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="60">
         <f t="shared" ref="C12:K12" si="0">SUM(C6:C11)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="60">
         <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="60">
         <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F12" s="60">
         <f t="shared" si="0"/>
         <v>1.1499999999999999</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="60">
         <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="H12" s="74">
+      <c r="H12" s="60">
         <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="I12" s="74">
+      <c r="I12" s="60">
         <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="J12" s="74">
+      <c r="J12" s="60">
         <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
-      <c r="K12" s="74">
+      <c r="K12" s="60">
         <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="104" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="104"/>
+      <c r="O14" s="104"/>
     </row>
     <row r="15" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="I15" s="45" t="s">
+      <c r="I15" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="J15" s="45" t="s">
+      <c r="J15" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="K15" s="45" t="s">
+      <c r="K15" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="L15" s="45" t="s">
+      <c r="L15" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="M15" s="45" t="s">
+      <c r="M15" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="N15" s="45" t="s">
+      <c r="N15" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="O15" s="45" t="s">
+      <c r="O15" s="31" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="75">
+      <c r="C16" s="61">
         <f>'Perhitungan MFEP'!P5</f>
         <v>1</v>
       </c>
-      <c r="D16" s="76" t="e">
+      <c r="D16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E16" s="76" t="e">
+      <c r="E16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F16" s="76" t="e">
+      <c r="F16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G16" s="76" t="e">
+      <c r="G16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H16" s="76" t="e">
+      <c r="H16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I16" s="76" t="e">
+      <c r="I16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J16" s="76" t="e">
+      <c r="J16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="76" t="e">
+      <c r="K16" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C5:H5,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L16" s="77" t="e">
+      <c r="L16" s="63" t="e">
         <f t="shared" ref="L16:L35" si="1">MIN(D16:K16)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M16" s="78" t="e">
+      <c r="M16" s="64" t="e">
         <f t="shared" ref="M16:M35" si="2">MAX(D16:K16)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N16" s="79" t="e">
+      <c r="N16" s="65" t="e">
         <f t="shared" ref="N16:N35" si="3">M16-L16</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O16" s="80" t="e">
+      <c r="O16" s="66" t="e">
         <f t="shared" ref="O16:O35" si="4">IF(N16&lt;0.05,"Stabil","Sensitif")</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="75">
+      <c r="C17" s="61">
         <f>'Perhitungan MFEP'!P6</f>
         <v>2</v>
       </c>
-      <c r="D17" s="81" t="e">
+      <c r="D17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E17" s="81" t="e">
+      <c r="E17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F17" s="81" t="e">
+      <c r="F17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G17" s="81" t="e">
+      <c r="G17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H17" s="81" t="e">
+      <c r="H17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I17" s="81" t="e">
+      <c r="I17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J17" s="81" t="e">
+      <c r="J17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="81" t="e">
+      <c r="K17" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C6:H6,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L17" s="77" t="e">
+      <c r="L17" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M17" s="78" t="e">
+      <c r="M17" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N17" s="79" t="e">
+      <c r="N17" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O17" s="82" t="e">
+      <c r="O17" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="75">
+      <c r="C18" s="61">
         <f>'Perhitungan MFEP'!P7</f>
         <v>6</v>
       </c>
-      <c r="D18" s="76" t="e">
+      <c r="D18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E18" s="76" t="e">
+      <c r="E18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="76" t="e">
+      <c r="F18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G18" s="76" t="e">
+      <c r="G18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="76" t="e">
+      <c r="H18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="76" t="e">
+      <c r="I18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="76" t="e">
+      <c r="J18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="76" t="e">
+      <c r="K18" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C7:H7,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L18" s="77" t="e">
+      <c r="L18" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M18" s="78" t="e">
+      <c r="M18" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N18" s="79" t="e">
+      <c r="N18" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O18" s="80" t="e">
+      <c r="O18" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="75">
+      <c r="C19" s="61">
         <f>'Perhitungan MFEP'!P8</f>
         <v>12</v>
       </c>
-      <c r="D19" s="81" t="e">
+      <c r="D19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E19" s="81" t="e">
+      <c r="E19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F19" s="81" t="e">
+      <c r="F19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G19" s="81" t="e">
+      <c r="G19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H19" s="81" t="e">
+      <c r="H19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I19" s="81" t="e">
+      <c r="I19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="81" t="e">
+      <c r="J19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="81" t="e">
+      <c r="K19" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C8:H8,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L19" s="77" t="e">
+      <c r="L19" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M19" s="78" t="e">
+      <c r="M19" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N19" s="79" t="e">
+      <c r="N19" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O19" s="82" t="e">
+      <c r="O19" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="61">
         <f>'Perhitungan MFEP'!P9</f>
         <v>14</v>
       </c>
-      <c r="D20" s="76" t="e">
+      <c r="D20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E20" s="76" t="e">
+      <c r="E20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F20" s="76" t="e">
+      <c r="F20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G20" s="76" t="e">
+      <c r="G20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H20" s="76" t="e">
+      <c r="H20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I20" s="76" t="e">
+      <c r="I20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J20" s="76" t="e">
+      <c r="J20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K20" s="76" t="e">
+      <c r="K20" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C9:H9,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L20" s="77" t="e">
+      <c r="L20" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M20" s="78" t="e">
+      <c r="M20" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N20" s="79" t="e">
+      <c r="N20" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O20" s="80" t="e">
+      <c r="O20" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="75">
+      <c r="C21" s="61">
         <f>'Perhitungan MFEP'!P10</f>
         <v>5</v>
       </c>
-      <c r="D21" s="81" t="e">
+      <c r="D21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E21" s="81" t="e">
+      <c r="E21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F21" s="81" t="e">
+      <c r="F21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G21" s="81" t="e">
+      <c r="G21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="81" t="e">
+      <c r="H21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I21" s="81" t="e">
+      <c r="I21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J21" s="81" t="e">
+      <c r="J21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K21" s="81" t="e">
+      <c r="K21" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C10:H10,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L21" s="77" t="e">
+      <c r="L21" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M21" s="78" t="e">
+      <c r="M21" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N21" s="79" t="e">
+      <c r="N21" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O21" s="82" t="e">
+      <c r="O21" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="75">
+      <c r="C22" s="61">
         <f>'Perhitungan MFEP'!P11</f>
         <v>17</v>
       </c>
-      <c r="D22" s="76" t="e">
+      <c r="D22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E22" s="76" t="e">
+      <c r="E22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F22" s="76" t="e">
+      <c r="F22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G22" s="76" t="e">
+      <c r="G22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="76" t="e">
+      <c r="H22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I22" s="76" t="e">
+      <c r="I22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J22" s="76" t="e">
+      <c r="J22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K22" s="76" t="e">
+      <c r="K22" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C11:H11,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L22" s="77" t="e">
+      <c r="L22" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M22" s="78" t="e">
+      <c r="M22" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N22" s="79" t="e">
+      <c r="N22" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O22" s="80" t="e">
+      <c r="O22" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="75">
+      <c r="C23" s="61">
         <f>'Perhitungan MFEP'!P12</f>
         <v>6</v>
       </c>
-      <c r="D23" s="81" t="e">
+      <c r="D23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E23" s="81" t="e">
+      <c r="E23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F23" s="81" t="e">
+      <c r="F23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G23" s="81" t="e">
+      <c r="G23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H23" s="81" t="e">
+      <c r="H23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I23" s="81" t="e">
+      <c r="I23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J23" s="81" t="e">
+      <c r="J23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K23" s="81" t="e">
+      <c r="K23" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C12:H12,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L23" s="77" t="e">
+      <c r="L23" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M23" s="78" t="e">
+      <c r="M23" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N23" s="79" t="e">
+      <c r="N23" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O23" s="82" t="e">
+      <c r="O23" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C24" s="75">
+      <c r="C24" s="61">
         <f>'Perhitungan MFEP'!P13</f>
         <v>20</v>
       </c>
-      <c r="D24" s="76" t="e">
+      <c r="D24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E24" s="76" t="e">
+      <c r="E24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F24" s="76" t="e">
+      <c r="F24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G24" s="76" t="e">
+      <c r="G24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H24" s="76" t="e">
+      <c r="H24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I24" s="76" t="e">
+      <c r="I24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J24" s="76" t="e">
+      <c r="J24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K24" s="76" t="e">
+      <c r="K24" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C13:H13,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L24" s="77" t="e">
+      <c r="L24" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M24" s="78" t="e">
+      <c r="M24" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N24" s="79" t="e">
+      <c r="N24" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O24" s="80" t="e">
+      <c r="O24" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="75">
+      <c r="C25" s="61">
         <f>'Perhitungan MFEP'!P14</f>
         <v>12</v>
       </c>
-      <c r="D25" s="81" t="e">
+      <c r="D25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E25" s="81" t="e">
+      <c r="E25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F25" s="81" t="e">
+      <c r="F25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G25" s="81" t="e">
+      <c r="G25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H25" s="81" t="e">
+      <c r="H25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I25" s="81" t="e">
+      <c r="I25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J25" s="81" t="e">
+      <c r="J25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K25" s="81" t="e">
+      <c r="K25" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C14:H14,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L25" s="77" t="e">
+      <c r="L25" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M25" s="78" t="e">
+      <c r="M25" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N25" s="79" t="e">
+      <c r="N25" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O25" s="82" t="e">
+      <c r="O25" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="75">
+      <c r="C26" s="61">
         <f>'Perhitungan MFEP'!P15</f>
         <v>2</v>
       </c>
-      <c r="D26" s="76" t="e">
+      <c r="D26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E26" s="76" t="e">
+      <c r="E26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="76" t="e">
+      <c r="F26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G26" s="76" t="e">
+      <c r="G26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H26" s="76" t="e">
+      <c r="H26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I26" s="76" t="e">
+      <c r="I26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J26" s="76" t="e">
+      <c r="J26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="76" t="e">
+      <c r="K26" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C15:H15,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L26" s="77" t="e">
+      <c r="L26" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M26" s="78" t="e">
+      <c r="M26" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N26" s="79" t="e">
+      <c r="N26" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O26" s="80" t="e">
+      <c r="O26" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="75">
+      <c r="C27" s="61">
         <f>'Perhitungan MFEP'!P16</f>
         <v>14</v>
       </c>
-      <c r="D27" s="81" t="e">
+      <c r="D27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E27" s="81" t="e">
+      <c r="E27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F27" s="81" t="e">
+      <c r="F27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G27" s="81" t="e">
+      <c r="G27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H27" s="81" t="e">
+      <c r="H27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I27" s="81" t="e">
+      <c r="I27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J27" s="81" t="e">
+      <c r="J27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K27" s="81" t="e">
+      <c r="K27" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C16:H16,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L27" s="77" t="e">
+      <c r="L27" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M27" s="78" t="e">
+      <c r="M27" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N27" s="79" t="e">
+      <c r="N27" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O27" s="82" t="e">
+      <c r="O27" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="C28" s="75">
+      <c r="C28" s="61">
         <f>'Perhitungan MFEP'!P17</f>
         <v>17</v>
       </c>
-      <c r="D28" s="76" t="e">
+      <c r="D28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E28" s="76" t="e">
+      <c r="E28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F28" s="76" t="e">
+      <c r="F28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G28" s="76" t="e">
+      <c r="G28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H28" s="76" t="e">
+      <c r="H28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I28" s="76" t="e">
+      <c r="I28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J28" s="76" t="e">
+      <c r="J28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K28" s="76" t="e">
+      <c r="K28" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C17:H17,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L28" s="77" t="e">
+      <c r="L28" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M28" s="78" t="e">
+      <c r="M28" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N28" s="79" t="e">
+      <c r="N28" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O28" s="80" t="e">
+      <c r="O28" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C29" s="75">
+      <c r="C29" s="61">
         <f>'Perhitungan MFEP'!P18</f>
         <v>16</v>
       </c>
-      <c r="D29" s="81" t="e">
+      <c r="D29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E29" s="81" t="e">
+      <c r="E29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F29" s="81" t="e">
+      <c r="F29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="81" t="e">
+      <c r="G29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H29" s="81" t="e">
+      <c r="H29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I29" s="81" t="e">
+      <c r="I29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="81" t="e">
+      <c r="J29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="81" t="e">
+      <c r="K29" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C18:H18,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L29" s="77" t="e">
+      <c r="L29" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M29" s="78" t="e">
+      <c r="M29" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N29" s="79" t="e">
+      <c r="N29" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="82" t="e">
+      <c r="O29" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="C30" s="75">
+      <c r="C30" s="61">
         <f>'Perhitungan MFEP'!P19</f>
         <v>11</v>
       </c>
-      <c r="D30" s="76" t="e">
+      <c r="D30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E30" s="76" t="e">
+      <c r="E30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="76" t="e">
+      <c r="F30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G30" s="76" t="e">
+      <c r="G30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H30" s="76" t="e">
+      <c r="H30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I30" s="76" t="e">
+      <c r="I30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J30" s="76" t="e">
+      <c r="J30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K30" s="76" t="e">
+      <c r="K30" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C19:H19,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L30" s="77" t="e">
+      <c r="L30" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M30" s="78" t="e">
+      <c r="M30" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N30" s="79" t="e">
+      <c r="N30" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O30" s="80" t="e">
+      <c r="O30" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C31" s="75">
+      <c r="C31" s="61">
         <f>'Perhitungan MFEP'!P20</f>
         <v>9</v>
       </c>
-      <c r="D31" s="81" t="e">
+      <c r="D31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E31" s="81" t="e">
+      <c r="E31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="81" t="e">
+      <c r="F31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G31" s="81" t="e">
+      <c r="G31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H31" s="81" t="e">
+      <c r="H31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I31" s="81" t="e">
+      <c r="I31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J31" s="81" t="e">
+      <c r="J31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K31" s="81" t="e">
+      <c r="K31" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C20:H20,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L31" s="77" t="e">
+      <c r="L31" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M31" s="78" t="e">
+      <c r="M31" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N31" s="79" t="e">
+      <c r="N31" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O31" s="82" t="e">
+      <c r="O31" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C32" s="75">
+      <c r="C32" s="61">
         <f>'Perhitungan MFEP'!P21</f>
         <v>17</v>
       </c>
-      <c r="D32" s="76" t="e">
+      <c r="D32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E32" s="76" t="e">
+      <c r="E32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="76" t="e">
+      <c r="F32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G32" s="76" t="e">
+      <c r="G32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="76" t="e">
+      <c r="H32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I32" s="76" t="e">
+      <c r="I32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J32" s="76" t="e">
+      <c r="J32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K32" s="76" t="e">
+      <c r="K32" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C21:H21,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L32" s="77" t="e">
+      <c r="L32" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M32" s="78" t="e">
+      <c r="M32" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N32" s="79" t="e">
+      <c r="N32" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O32" s="80" t="e">
+      <c r="O32" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C33" s="75">
+      <c r="C33" s="61">
         <f>'Perhitungan MFEP'!P22</f>
         <v>9</v>
       </c>
-      <c r="D33" s="81" t="e">
+      <c r="D33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E33" s="81" t="e">
+      <c r="E33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F33" s="81" t="e">
+      <c r="F33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G33" s="81" t="e">
+      <c r="G33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H33" s="81" t="e">
+      <c r="H33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I33" s="81" t="e">
+      <c r="I33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J33" s="81" t="e">
+      <c r="J33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K33" s="81" t="e">
+      <c r="K33" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C22:H22,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L33" s="77" t="e">
+      <c r="L33" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M33" s="78" t="e">
+      <c r="M33" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N33" s="79" t="e">
+      <c r="N33" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O33" s="82" t="e">
+      <c r="O33" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="75">
+      <c r="C34" s="61">
         <f>'Perhitungan MFEP'!P23</f>
         <v>6</v>
       </c>
-      <c r="D34" s="76" t="e">
+      <c r="D34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E34" s="76" t="e">
+      <c r="E34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F34" s="76" t="e">
+      <c r="F34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G34" s="76" t="e">
+      <c r="G34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H34" s="76" t="e">
+      <c r="H34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I34" s="76" t="e">
+      <c r="I34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J34" s="76" t="e">
+      <c r="J34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K34" s="76" t="e">
+      <c r="K34" s="62" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C23:H23,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L34" s="77" t="e">
+      <c r="L34" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M34" s="78" t="e">
+      <c r="M34" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N34" s="79" t="e">
+      <c r="N34" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O34" s="80" t="e">
+      <c r="O34" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C35" s="75">
+      <c r="C35" s="61">
         <f>'Perhitungan MFEP'!P24</f>
         <v>4</v>
       </c>
-      <c r="D35" s="81" t="e">
+      <c r="D35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(D6:D11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E35" s="81" t="e">
+      <c r="E35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(E6:E11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F35" s="81" t="e">
+      <c r="F35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(F6:F11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G35" s="81" t="e">
+      <c r="G35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(G6:G11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H35" s="81" t="e">
+      <c r="H35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(H6:H11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I35" s="81" t="e">
+      <c r="I35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(I6:I11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J35" s="81" t="e">
+      <c r="J35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(J6:J11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K35" s="81" t="e">
+      <c r="K35" s="67" t="e">
         <f>SUMPRODUCT('Perhitungan MFEP'!C24:H24,TRANSPOSE(K6:K11))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L35" s="77" t="e">
+      <c r="L35" s="63" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M35" s="78" t="e">
+      <c r="M35" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N35" s="79" t="e">
+      <c r="N35" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O35" s="82" t="e">
+      <c r="O35" s="68" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
@@ -6381,12 +6375,12 @@
     <mergeCell ref="A14:O14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H42"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6399,881 +6393,891 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="123" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
     </row>
     <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="104" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="31" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83">
+      <c r="A5" s="69">
         <f>'Perhitungan MFEP'!P5</f>
         <v>1</v>
       </c>
-      <c r="B5" s="84" t="str">
+      <c r="B5" s="70" t="str">
         <f>'Perhitungan MFEP'!B5</f>
         <v>Timlo Sastro</v>
       </c>
-      <c r="C5" s="85" t="str">
+      <c r="C5" s="71" t="str">
         <f>'Data Destinasi'!A4</f>
         <v>D01</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="72">
         <f>'Perhitungan MFEP'!O5</f>
         <v>0.96000000000000019</v>
       </c>
-      <c r="E5" s="87" t="s">
+      <c r="E5" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="G5" s="88" t="s">
+      <c r="G5" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="H5" s="88" t="s">
+      <c r="H5" s="74" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83">
+      <c r="A6" s="69">
         <f>'Perhitungan MFEP'!P6</f>
         <v>2</v>
       </c>
-      <c r="B6" s="84" t="str">
+      <c r="B6" s="70" t="str">
         <f>'Perhitungan MFEP'!B6</f>
         <v>Nasi Liwet Bu Wongso Lemu</v>
       </c>
-      <c r="C6" s="85" t="str">
+      <c r="C6" s="71" t="str">
         <f>'Data Destinasi'!A5</f>
         <v>D02</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="72">
         <f>'Perhitungan MFEP'!O6</f>
         <v>0.93000000000000016</v>
       </c>
-      <c r="E6" s="87" t="s">
+      <c r="E6" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="F6" s="88" t="s">
+      <c r="F6" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="G6" s="88" t="s">
+      <c r="G6" s="74" t="s">
         <v>222</v>
       </c>
-      <c r="H6" s="88" t="s">
+      <c r="H6" s="74" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="83">
+      <c r="A7" s="69">
         <f>'Perhitungan MFEP'!P7</f>
         <v>6</v>
       </c>
-      <c r="B7" s="84" t="str">
+      <c r="B7" s="70" t="str">
         <f>'Perhitungan MFEP'!B7</f>
         <v>Selat Solo Mbak Lies</v>
       </c>
-      <c r="C7" s="85" t="str">
+      <c r="C7" s="71" t="str">
         <f>'Data Destinasi'!A6</f>
         <v>D03</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="72">
         <f>'Perhitungan MFEP'!O7</f>
         <v>0.89000000000000012</v>
       </c>
-      <c r="E7" s="87" t="s">
+      <c r="E7" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="F7" s="88" t="s">
+      <c r="F7" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="G7" s="88" t="s">
+      <c r="G7" s="74" t="s">
         <v>225</v>
       </c>
-      <c r="H7" s="88" t="s">
+      <c r="H7" s="74" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="89">
+      <c r="A8" s="75">
         <f>'Perhitungan MFEP'!P8</f>
         <v>12</v>
       </c>
-      <c r="B8" s="90" t="str">
+      <c r="B8" s="76" t="str">
         <f>'Perhitungan MFEP'!B8</f>
         <v>Soto Gading</v>
       </c>
-      <c r="C8" s="91" t="str">
+      <c r="C8" s="77" t="str">
         <f>'Data Destinasi'!A7</f>
         <v>D04</v>
       </c>
-      <c r="D8" s="92">
+      <c r="D8" s="78">
         <f>'Perhitungan MFEP'!O8</f>
         <v>0.81</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="79" t="s">
         <v>227</v>
       </c>
-      <c r="F8" s="94" t="s">
+      <c r="F8" s="80" t="s">
         <v>228</v>
       </c>
-      <c r="G8" s="94" t="s">
+      <c r="G8" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="H8" s="94" t="s">
+      <c r="H8" s="80" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="89">
+      <c r="A9" s="75">
         <f>'Perhitungan MFEP'!P9</f>
         <v>14</v>
       </c>
-      <c r="B9" s="90" t="str">
+      <c r="B9" s="76" t="str">
         <f>'Perhitungan MFEP'!B9</f>
         <v>Wedangan Jadul Pak Gareng</v>
       </c>
-      <c r="C9" s="91" t="str">
+      <c r="C9" s="77" t="str">
         <f>'Data Destinasi'!A8</f>
         <v>D05</v>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="78">
         <f>'Perhitungan MFEP'!O9</f>
         <v>0.8</v>
       </c>
-      <c r="E9" s="93" t="s">
+      <c r="E9" s="79" t="s">
         <v>227</v>
       </c>
-      <c r="F9" s="94" t="s">
+      <c r="F9" s="80" t="s">
         <v>231</v>
       </c>
-      <c r="G9" s="94" t="s">
+      <c r="G9" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="H9" s="94" t="s">
+      <c r="H9" s="80" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="89">
+      <c r="A10" s="75">
         <f>'Perhitungan MFEP'!P10</f>
         <v>5</v>
       </c>
-      <c r="B10" s="90" t="str">
+      <c r="B10" s="76" t="str">
         <f>'Perhitungan MFEP'!B10</f>
         <v>Pasar Gede – Zona Kuliner</v>
       </c>
-      <c r="C10" s="91" t="str">
+      <c r="C10" s="77" t="str">
         <f>'Data Destinasi'!A9</f>
         <v>D06</v>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="78">
         <f>'Perhitungan MFEP'!O10</f>
         <v>0.91</v>
       </c>
-      <c r="E10" s="93" t="s">
+      <c r="E10" s="79" t="s">
         <v>227</v>
       </c>
-      <c r="F10" s="94" t="s">
+      <c r="F10" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="G10" s="94" t="s">
+      <c r="G10" s="80" t="s">
         <v>235</v>
       </c>
-      <c r="H10" s="94" t="s">
+      <c r="H10" s="80" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="95">
+      <c r="A11" s="81">
         <f>'Perhitungan MFEP'!P11</f>
         <v>17</v>
       </c>
-      <c r="B11" s="96" t="str">
+      <c r="B11" s="82" t="str">
         <f>'Perhitungan MFEP'!B11</f>
         <v>Nasi Gudeg Bu Semi</v>
       </c>
-      <c r="C11" s="97" t="str">
+      <c r="C11" s="83" t="str">
         <f>'Data Destinasi'!A10</f>
         <v>D07</v>
       </c>
-      <c r="D11" s="98">
+      <c r="D11" s="84">
         <f>'Perhitungan MFEP'!O11</f>
         <v>0.76000000000000023</v>
       </c>
-      <c r="E11" s="99" t="s">
+      <c r="E11" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="F11" s="100" t="s">
+      <c r="F11" s="86" t="s">
         <v>238</v>
       </c>
-      <c r="G11" s="100" t="s">
+      <c r="G11" s="86" t="s">
         <v>239</v>
       </c>
-      <c r="H11" s="100" t="s">
+      <c r="H11" s="86" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95">
+      <c r="A12" s="81">
         <f>'Perhitungan MFEP'!P12</f>
         <v>6</v>
       </c>
-      <c r="B12" s="96" t="str">
+      <c r="B12" s="82" t="str">
         <f>'Perhitungan MFEP'!B12</f>
         <v>Dawet Telasih Bu Dermi</v>
       </c>
-      <c r="C12" s="97" t="str">
+      <c r="C12" s="83" t="str">
         <f>'Data Destinasi'!A11</f>
         <v>D08</v>
       </c>
-      <c r="D12" s="98">
+      <c r="D12" s="84">
         <f>'Perhitungan MFEP'!O12</f>
         <v>0.89000000000000012</v>
       </c>
-      <c r="E12" s="99" t="s">
+      <c r="E12" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="F12" s="100" t="s">
+      <c r="F12" s="86" t="s">
         <v>241</v>
       </c>
-      <c r="G12" s="100" t="s">
+      <c r="G12" s="86" t="s">
         <v>242</v>
       </c>
-      <c r="H12" s="100" t="s">
+      <c r="H12" s="86" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="95">
+      <c r="A13" s="81">
         <f>'Perhitungan MFEP'!P13</f>
         <v>20</v>
       </c>
-      <c r="B13" s="96" t="str">
+      <c r="B13" s="82" t="str">
         <f>'Perhitungan MFEP'!B13</f>
         <v>Intip Goreng Pak Slamet</v>
       </c>
-      <c r="C13" s="97" t="str">
+      <c r="C13" s="83" t="str">
         <f>'Data Destinasi'!A12</f>
         <v>D09</v>
       </c>
-      <c r="D13" s="98">
+      <c r="D13" s="84">
         <f>'Perhitungan MFEP'!O13</f>
         <v>0.76</v>
       </c>
-      <c r="E13" s="99" t="s">
+      <c r="E13" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="F13" s="100" t="s">
+      <c r="F13" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="G13" s="100" t="s">
+      <c r="G13" s="86" t="s">
         <v>245</v>
       </c>
-      <c r="H13" s="100" t="s">
+      <c r="H13" s="86" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="95">
+      <c r="A14" s="81">
         <f>'Perhitungan MFEP'!P14</f>
         <v>12</v>
       </c>
-      <c r="B14" s="96" t="str">
+      <c r="B14" s="82" t="str">
         <f>'Perhitungan MFEP'!B14</f>
         <v>Sate Buntel Mbok Galak</v>
       </c>
-      <c r="C14" s="97" t="str">
+      <c r="C14" s="83" t="str">
         <f>'Data Destinasi'!A13</f>
         <v>D10</v>
       </c>
-      <c r="D14" s="98">
+      <c r="D14" s="84">
         <f>'Perhitungan MFEP'!O14</f>
         <v>0.81</v>
       </c>
-      <c r="E14" s="99" t="s">
+      <c r="E14" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="86" t="s">
         <v>247</v>
       </c>
-      <c r="G14" s="100" t="s">
+      <c r="G14" s="86" t="s">
         <v>248</v>
       </c>
-      <c r="H14" s="100" t="s">
+      <c r="H14" s="86" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="101">
+      <c r="A15" s="87">
         <f>'Perhitungan MFEP'!P15</f>
         <v>2</v>
       </c>
-      <c r="B15" s="102" t="str">
+      <c r="B15" s="88" t="str">
         <f>'Perhitungan MFEP'!B15</f>
         <v>Tengkleng Bu Edi</v>
       </c>
-      <c r="C15" s="103" t="str">
+      <c r="C15" s="89" t="str">
         <f>'Data Destinasi'!A14</f>
         <v>D11</v>
       </c>
-      <c r="D15" s="104">
+      <c r="D15" s="90">
         <f>'Perhitungan MFEP'!O15</f>
         <v>0.93000000000000016</v>
       </c>
-      <c r="E15" s="105" t="s">
+      <c r="E15" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="106" t="s">
+      <c r="F15" s="92" t="s">
         <v>251</v>
       </c>
-      <c r="G15" s="106" t="s">
+      <c r="G15" s="92" t="s">
         <v>252</v>
       </c>
-      <c r="H15" s="106" t="s">
+      <c r="H15" s="92" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="101">
+      <c r="A16" s="87">
         <f>'Perhitungan MFEP'!P16</f>
         <v>14</v>
       </c>
-      <c r="B16" s="102" t="str">
+      <c r="B16" s="88" t="str">
         <f>'Perhitungan MFEP'!B16</f>
         <v>Cabuk Rambak Pak Birin</v>
       </c>
-      <c r="C16" s="103" t="str">
+      <c r="C16" s="89" t="str">
         <f>'Data Destinasi'!A15</f>
         <v>D12</v>
       </c>
-      <c r="D16" s="104">
+      <c r="D16" s="90">
         <f>'Perhitungan MFEP'!O16</f>
         <v>0.8</v>
       </c>
-      <c r="E16" s="105" t="s">
+      <c r="E16" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="106" t="s">
+      <c r="F16" s="92" t="s">
         <v>254</v>
       </c>
-      <c r="G16" s="106" t="s">
+      <c r="G16" s="92" t="s">
         <v>255</v>
       </c>
-      <c r="H16" s="106" t="s">
+      <c r="H16" s="92" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="101">
+      <c r="A17" s="87">
         <f>'Perhitungan MFEP'!P17</f>
         <v>17</v>
       </c>
-      <c r="B17" s="102" t="str">
+      <c r="B17" s="88" t="str">
         <f>'Perhitungan MFEP'!B17</f>
         <v>Roti Mandarin Orion</v>
       </c>
-      <c r="C17" s="103" t="str">
+      <c r="C17" s="89" t="str">
         <f>'Data Destinasi'!A16</f>
         <v>D13</v>
       </c>
-      <c r="D17" s="104">
+      <c r="D17" s="90">
         <f>'Perhitungan MFEP'!O17</f>
         <v>0.76000000000000023</v>
       </c>
-      <c r="E17" s="105" t="s">
+      <c r="E17" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="92" t="s">
         <v>257</v>
       </c>
-      <c r="G17" s="106" t="s">
+      <c r="G17" s="92" t="s">
         <v>258</v>
       </c>
-      <c r="H17" s="106" t="s">
+      <c r="H17" s="92" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="101">
+      <c r="A18" s="87">
         <f>'Perhitungan MFEP'!P18</f>
         <v>16</v>
       </c>
-      <c r="B18" s="102" t="str">
+      <c r="B18" s="88" t="str">
         <f>'Perhitungan MFEP'!B18</f>
         <v>Wedang Ronde Pak Min</v>
       </c>
-      <c r="C18" s="103" t="str">
+      <c r="C18" s="89" t="str">
         <f>'Data Destinasi'!A17</f>
         <v>D14</v>
       </c>
-      <c r="D18" s="104">
+      <c r="D18" s="90">
         <f>'Perhitungan MFEP'!O18</f>
         <v>0.78000000000000025</v>
       </c>
-      <c r="E18" s="105" t="s">
+      <c r="E18" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="F18" s="106" t="s">
+      <c r="F18" s="92" t="s">
         <v>260</v>
       </c>
-      <c r="G18" s="106" t="s">
+      <c r="G18" s="92" t="s">
         <v>261</v>
       </c>
-      <c r="H18" s="106" t="s">
+      <c r="H18" s="92" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="101">
+      <c r="A19" s="87">
         <f>'Perhitungan MFEP'!P19</f>
         <v>11</v>
       </c>
-      <c r="B19" s="102" t="str">
+      <c r="B19" s="88" t="str">
         <f>'Perhitungan MFEP'!B19</f>
         <v>Jenang Mirah</v>
       </c>
-      <c r="C19" s="103" t="str">
+      <c r="C19" s="89" t="str">
         <f>'Data Destinasi'!A18</f>
         <v>D15</v>
       </c>
-      <c r="D19" s="104">
+      <c r="D19" s="90">
         <f>'Perhitungan MFEP'!O19</f>
         <v>0.82000000000000006</v>
       </c>
-      <c r="E19" s="105" t="s">
+      <c r="E19" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="F19" s="106" t="s">
+      <c r="F19" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="G19" s="106" t="s">
+      <c r="G19" s="92" t="s">
         <v>264</v>
       </c>
-      <c r="H19" s="106" t="s">
+      <c r="H19" s="92" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="107">
+      <c r="A20" s="93">
         <f>'Perhitungan MFEP'!P20</f>
         <v>9</v>
       </c>
-      <c r="B20" s="108" t="str">
+      <c r="B20" s="94" t="str">
         <f>'Perhitungan MFEP'!B20</f>
         <v>Gempol Pleret Bu Sari</v>
       </c>
-      <c r="C20" s="109" t="str">
+      <c r="C20" s="95" t="str">
         <f>'Data Destinasi'!A19</f>
         <v>D16</v>
       </c>
-      <c r="D20" s="110">
+      <c r="D20" s="96">
         <f>'Perhitungan MFEP'!O20</f>
         <v>0.84000000000000008</v>
       </c>
-      <c r="E20" s="111" t="s">
+      <c r="E20" s="97" t="s">
         <v>266</v>
       </c>
-      <c r="F20" s="112" t="s">
+      <c r="F20" s="98" t="s">
         <v>267</v>
       </c>
-      <c r="G20" s="112" t="s">
+      <c r="G20" s="98" t="s">
         <v>268</v>
       </c>
-      <c r="H20" s="112" t="s">
+      <c r="H20" s="98" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="107">
+      <c r="A21" s="93">
         <f>'Perhitungan MFEP'!P21</f>
         <v>17</v>
       </c>
-      <c r="B21" s="108" t="str">
+      <c r="B21" s="94" t="str">
         <f>'Perhitungan MFEP'!B21</f>
         <v>Sego Pecel Bu Tun</v>
       </c>
-      <c r="C21" s="109" t="str">
+      <c r="C21" s="95" t="str">
         <f>'Data Destinasi'!A20</f>
         <v>D17</v>
       </c>
-      <c r="D21" s="110">
+      <c r="D21" s="96">
         <f>'Perhitungan MFEP'!O21</f>
         <v>0.76000000000000023</v>
       </c>
-      <c r="E21" s="111" t="s">
+      <c r="E21" s="97" t="s">
         <v>266</v>
       </c>
-      <c r="F21" s="112" t="s">
+      <c r="F21" s="98" t="s">
         <v>270</v>
       </c>
-      <c r="G21" s="112" t="s">
+      <c r="G21" s="98" t="s">
         <v>271</v>
       </c>
-      <c r="H21" s="112" t="s">
+      <c r="H21" s="98" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="107">
+      <c r="A22" s="93">
         <f>'Perhitungan MFEP'!P22</f>
         <v>9</v>
       </c>
-      <c r="B22" s="108" t="str">
+      <c r="B22" s="94" t="str">
         <f>'Perhitungan MFEP'!B22</f>
         <v>Garang Asem Bu Sulastri</v>
       </c>
-      <c r="C22" s="109" t="str">
+      <c r="C22" s="95" t="str">
         <f>'Data Destinasi'!A21</f>
         <v>D18</v>
       </c>
-      <c r="D22" s="110">
+      <c r="D22" s="96">
         <f>'Perhitungan MFEP'!O22</f>
         <v>0.84000000000000008</v>
       </c>
-      <c r="E22" s="111" t="s">
+      <c r="E22" s="97" t="s">
         <v>266</v>
       </c>
-      <c r="F22" s="112" t="s">
+      <c r="F22" s="98" t="s">
         <v>273</v>
       </c>
-      <c r="G22" s="112" t="s">
+      <c r="G22" s="98" t="s">
         <v>274</v>
       </c>
-      <c r="H22" s="112" t="s">
+      <c r="H22" s="98" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="107">
+      <c r="A23" s="93">
         <f>'Perhitungan MFEP'!P23</f>
         <v>6</v>
       </c>
-      <c r="B23" s="108" t="str">
+      <c r="B23" s="94" t="str">
         <f>'Perhitungan MFEP'!B23</f>
         <v>Bestik Jawa Pak Maryanto</v>
       </c>
-      <c r="C23" s="109" t="str">
+      <c r="C23" s="95" t="str">
         <f>'Data Destinasi'!A22</f>
         <v>D19</v>
       </c>
-      <c r="D23" s="110">
+      <c r="D23" s="96">
         <f>'Perhitungan MFEP'!O23</f>
         <v>0.89000000000000012</v>
       </c>
-      <c r="E23" s="111" t="s">
+      <c r="E23" s="97" t="s">
         <v>266</v>
       </c>
-      <c r="F23" s="112" t="s">
+      <c r="F23" s="98" t="s">
         <v>276</v>
       </c>
-      <c r="G23" s="112" t="s">
+      <c r="G23" s="98" t="s">
         <v>277</v>
       </c>
-      <c r="H23" s="112" t="s">
+      <c r="H23" s="98" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="107">
+      <c r="A24" s="93">
         <f>'Perhitungan MFEP'!P24</f>
         <v>4</v>
       </c>
-      <c r="B24" s="108" t="str">
+      <c r="B24" s="94" t="str">
         <f>'Perhitungan MFEP'!B24</f>
         <v>Pasar Triwindu – Kuliner Heritage</v>
       </c>
-      <c r="C24" s="109" t="str">
+      <c r="C24" s="95" t="str">
         <f>'Data Destinasi'!A23</f>
         <v>D20</v>
       </c>
-      <c r="D24" s="110">
+      <c r="D24" s="96">
         <f>'Perhitungan MFEP'!O24</f>
         <v>0.91999999999999993</v>
       </c>
-      <c r="E24" s="111" t="s">
+      <c r="E24" s="97" t="s">
         <v>266</v>
       </c>
-      <c r="F24" s="112" t="s">
+      <c r="F24" s="98" t="s">
         <v>279</v>
       </c>
-      <c r="G24" s="112" t="s">
+      <c r="G24" s="98" t="s">
         <v>280</v>
       </c>
-      <c r="H24" s="112" t="s">
+      <c r="H24" s="98" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="104" t="s">
         <v>282</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="104"/>
     </row>
     <row r="27" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="118" t="s">
+      <c r="B27" s="124" t="s">
         <v>283</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="118"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="124"/>
     </row>
     <row r="28" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="93" t="s">
+      <c r="A28" s="79" t="s">
         <v>227</v>
       </c>
-      <c r="B28" s="119" t="s">
+      <c r="B28" s="125" t="s">
         <v>284</v>
       </c>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
     </row>
     <row r="29" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="99" t="s">
+      <c r="A29" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="B29" s="120" t="s">
+      <c r="B29" s="119" t="s">
         <v>285</v>
       </c>
-      <c r="C29" s="120"/>
-      <c r="D29" s="120"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="120"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
     </row>
     <row r="30" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="105" t="s">
+      <c r="A30" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="B30" s="121" t="s">
+      <c r="B30" s="120" t="s">
         <v>286</v>
       </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="121"/>
-      <c r="G30" s="121"/>
-      <c r="H30" s="121"/>
+      <c r="C30" s="120"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="120"/>
     </row>
     <row r="31" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="111" t="s">
+      <c r="A31" s="97" t="s">
         <v>266</v>
       </c>
-      <c r="B31" s="122" t="s">
+      <c r="B31" s="121" t="s">
         <v>287</v>
       </c>
-      <c r="C31" s="122"/>
-      <c r="D31" s="122"/>
-      <c r="E31" s="122"/>
-      <c r="F31" s="122"/>
-      <c r="G31" s="122"/>
-      <c r="H31" s="122"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="121"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="121"/>
+      <c r="H31" s="121"/>
     </row>
     <row r="33" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="104" t="s">
         <v>288</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
+      <c r="B33" s="104"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
     </row>
     <row r="34" spans="1:8" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="113" t="s">
+      <c r="A34" s="99" t="s">
         <v>289</v>
       </c>
-      <c r="B34" s="113" t="s">
+      <c r="B34" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="123" t="s">
+      <c r="C34" s="122" t="s">
         <v>290</v>
       </c>
-      <c r="D34" s="123"/>
-      <c r="E34" s="123"/>
-      <c r="F34" s="123"/>
-      <c r="G34" s="123"/>
-      <c r="H34" s="123"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="122"/>
+      <c r="F34" s="122"/>
+      <c r="G34" s="122"/>
+      <c r="H34" s="122"/>
     </row>
     <row r="35" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="B35" s="114">
+      <c r="B35" s="100">
         <f>COUNTA('Data Destinasi'!B4:B23)</f>
         <v>20</v>
       </c>
-      <c r="C35" s="124" t="s">
+      <c r="C35" s="118" t="s">
         <v>292</v>
       </c>
-      <c r="D35" s="124"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="124"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="124"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="118"/>
     </row>
     <row r="36" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B36" s="115">
+      <c r="B36" s="101">
         <f>MAX('Perhitungan MFEP'!O5:O24)</f>
         <v>0.96000000000000019</v>
       </c>
-      <c r="C36" s="125" t="s">
+      <c r="C36" s="117" t="s">
         <v>294</v>
       </c>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="125"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
     </row>
     <row r="37" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="B37" s="115">
+      <c r="B37" s="101">
         <f>MIN('Perhitungan MFEP'!O5:O24)</f>
         <v>0.76</v>
       </c>
-      <c r="C37" s="124" t="s">
+      <c r="C37" s="118" t="s">
         <v>296</v>
       </c>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="124"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
     </row>
     <row r="38" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B38" s="115">
+      <c r="B38" s="101">
         <f>AVERAGE('Perhitungan MFEP'!O5:O24)</f>
         <v>0.84300000000000019</v>
       </c>
-      <c r="C38" s="125" t="s">
+      <c r="C38" s="117" t="s">
         <v>298</v>
       </c>
-      <c r="D38" s="125"/>
-      <c r="E38" s="125"/>
-      <c r="F38" s="125"/>
-      <c r="G38" s="125"/>
-      <c r="H38" s="125"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="117"/>
     </row>
     <row r="39" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="B39" s="115">
+      <c r="B39" s="101">
         <f>STDEV('Perhitungan MFEP'!O5:O24)</f>
         <v>6.6419718061494493E-2</v>
       </c>
-      <c r="C39" s="124" t="s">
+      <c r="C39" s="118" t="s">
         <v>300</v>
       </c>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="124"/>
-      <c r="G39" s="124"/>
-      <c r="H39" s="124"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="118"/>
     </row>
     <row r="40" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="B40" s="115">
+      <c r="B40" s="101">
         <f>COUNTIF(E5:E24,"Unggulan Heritage")</f>
         <v>3</v>
       </c>
-      <c r="C40" s="125" t="s">
+      <c r="C40" s="117" t="s">
         <v>302</v>
       </c>
-      <c r="D40" s="125"/>
-      <c r="E40" s="125"/>
-      <c r="F40" s="125"/>
-      <c r="G40" s="125"/>
-      <c r="H40" s="125"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
     </row>
     <row r="42" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="110" t="s">
         <v>303</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
+      <c r="B42" s="110"/>
+      <c r="C42" s="110"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="110"/>
+      <c r="G42" s="110"/>
+      <c r="H42" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="C34:H34"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="C35:H35"/>
@@ -7281,16 +7285,6 @@
     <mergeCell ref="C37:H37"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="C39:H39"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
